--- a/协作/30-风险登记册.xlsx
+++ b/协作/30-风险登记册.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -808,21 +808,73 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>风险-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>全开初期交付物负担偏重：每个切片都要维护 37+3 份</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>用「全开≠九个人」降低人力占用；40 份骨架一次性铺满，之后只追加增量；小型切片可用一个切片覆盖多条契约</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>开放</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"技术,进度,质量,供应链,合规"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="E2:E121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="F2:F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="I2:I121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"开放,已缓解,已发生,已关闭"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/30-风险登记册.xlsx
+++ b/协作/30-风险登记册.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -857,6 +857,58 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>风险-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DCG 引用外部 TEAMODEL 仓库：若跟踪 main 或脚本地更新，会协议版本漂移</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>流程</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>按标签固定引用（当前 tm-v3.5.1）；协议升版必须走一次变更记录并更新 01 画像的版本号；不跟踪 main</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>开放</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
         </is>
       </c>
     </row>
